--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>44008</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>44847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45999</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>45037</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>46095</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>45168</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>45170</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>45845</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>45890</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>46001</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>45351</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45530</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45981</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45768</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>45218</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>45719</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>45722</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>46091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44862</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>44876</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>44533</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>44749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>44805</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>44510</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>44855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>44809</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>44603</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44862</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44886</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>44862</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>44532</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44572</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>44580</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>44746</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>44608</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>44844</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>44852</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>44862</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>44857</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>44518</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44833</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>44662</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>44853</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>44791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>44468</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>44789</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>44790</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44533</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>44664</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>44502</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44541</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44624</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44700</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44789</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44861</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>45775</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>45094</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45698</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44664</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>45086</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45252</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44952</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>45201</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>45037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45320</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45212</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45350</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44988</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45764</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45098</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45198</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45534</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>45518</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45646</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44476</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>45106</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>45634</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45634</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>45455</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>45094</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>45321</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>45001</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45040</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>44781</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45067</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45237</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>45267</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44509</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45228</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45671</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44995</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45167</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45679</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45671</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>45371</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45102</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44501</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45371</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45547</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45302</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44838</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44893</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45879</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45365</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44929</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44866</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>44642</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45226</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45110</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45884</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45726</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45252</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>45524</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44991</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45460</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45211</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45634</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45247</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45903</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45433</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45905</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45534</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45053</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45706</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44991</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45593</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45315</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44957</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>45315</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44820</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45015</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45419</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44935</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>45320</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>45054</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>45694</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44935</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>44951</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>45166</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>45747</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44970</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45946</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44866</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>45953</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45953</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>45957</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45953</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45953</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45771</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45954</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45338</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>45959</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45959</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45170</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45632</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>45632</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>45534</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45964</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44886</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45966</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45209</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>46125</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45967</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45204</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45971</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45197</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>45975</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45975</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44656</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45975</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45407</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45407</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>45301</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45607</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45978</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44826</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45981</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45981</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45315</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44505</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>45986</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45446</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45719</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>45986</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>45989</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45407</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45669</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45993</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45607</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45226</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45067</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>46164</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>46165</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45240</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45771</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>46008</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>45546</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>44601</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>45755</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>46010</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>46168</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>46014</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>46014</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45084</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>46014</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>46014</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45037</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45281</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>46017</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>45237</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45601</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44830</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>44806</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45469</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45534</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45163</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>45660</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45127</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44475</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>45411</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45253</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>44510</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45268</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45341</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45355</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>46066</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>46066</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>46066</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>45252</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>46070</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>46070</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45161</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45541</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45079</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45061</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45748</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45238</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45244</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45211</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>46087</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45301</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45274</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>46191</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>44872</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>46097</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45008</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46191</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>46101</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>46101</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45104</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45170</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>46101</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>44590</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>46108</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45623</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45611</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44896</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45238</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44972</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45146</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45454</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>45601</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45253</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45111</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>46125</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>46125</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45029</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45148</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45160</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>44942</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45334</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45785</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45267</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>44944</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45427</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>44651</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>44964</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45210</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45985</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45094</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45694</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45694</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45695</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>44839</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>45623</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45704</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45317</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>46251</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45371</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45371</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44469</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44830</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45275</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>44883</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45261</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44475</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45301</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45532</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45015</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45758</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45334</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45118</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45685</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45607</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>46099</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45066</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45448</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45607</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>46260</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>46260</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>46260</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45366</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45198</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>46266</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>46266</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45267</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>46266</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45211</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45104</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>46226</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>46273</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46248</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>46248</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>46248</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45223</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>46272</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45414</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>46274</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>45644</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45573</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>46276</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45448</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45646</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45725</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45412</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45791</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45611</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45791</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45646</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>45733</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45733</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45548</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         <v>46282</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>45727</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45825</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45833</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45833</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>45832</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>45833</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>45764</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45839</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>45418</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>45110</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44474</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45329</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>44833</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45881</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44882</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45139</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45063</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45063</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45173</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>45152</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>44558</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>45152</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45620</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45600</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45141</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45762</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45776</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45786</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45785</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45794</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45794</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45712</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45712</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>45818</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>45840</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45985</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45985</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45985</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>46073</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>46091</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>46091</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>46106</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>46119</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>46125</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>44008</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>46095</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>45037</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45722</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45719</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45890</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>46085</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>45981</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45168</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>46001</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45768</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>46266</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45170</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45218</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45646</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>46091</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44862</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44876</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44749</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>44805</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44510</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44809</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44573</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44886</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44862</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44532</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44580</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44826</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44746</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44608</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44844</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44869</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44862</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44857</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44833</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44662</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44853</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44468</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>44789</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44533</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44565</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>44664</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44502</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44541</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>44624</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44700</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44816</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44798</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44789</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44861</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45198</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45669</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45334</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45198</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45338</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44781</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44475</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45211</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45448</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>45446</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45454</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45253</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45365</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44883</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45881</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>46014</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>46017</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45244</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45160</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45455</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45733</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45733</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45546</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44475</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44951</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45884</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45646</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>45110</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45548</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45726</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44972</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45460</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45727</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45534</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45903</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45905</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45660</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45910</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44896</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45706</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45001</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>46066</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>46066</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>46066</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>46070</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45127</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>46070</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45671</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44590</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45320</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45320</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>44942</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45209</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44944</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>46087</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45541</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45061</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45037</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45601</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>46097</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45698</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45946</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>46101</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45524</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>46101</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>46101</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45953</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45953</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45954</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45953</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45953</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46108</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45957</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45959</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45959</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>46125</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45593</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>46125</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45106</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45623</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45966</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>44509</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45967</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44991</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45971</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45978</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45975</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45975</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45975</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44970</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45679</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45981</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45981</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45685</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45879</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45098</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45989</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45634</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45247</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45985</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45993</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44991</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44820</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45067</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44501</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45748</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>46008</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>46010</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45785</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>46014</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46014</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45695</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>46014</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>44957</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45274</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45240</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45825</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44886</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45079</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44866</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45015</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45111</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45267</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45066</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45427</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45832</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45833</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45252</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45086</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44839</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45833</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45833</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>46125</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45094</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45764</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>44826</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45094</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45839</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45104</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44510</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46164</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45118</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44505</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>46168</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45418</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>46165</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45371</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45267</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45329</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>44474</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45146</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45110</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44833</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45148</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45771</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45166</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45607</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45607</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45534</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45037</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45634</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45634</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45469</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45104</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>44476</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>46184</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45518</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45170</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45607</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46191</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45040</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45758</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45534</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>46191</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45355</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45411</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45632</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45632</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45054</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45067</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>44601</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45084</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44610</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45281</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45204</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45371</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45407</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46251</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45163</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45170</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45201</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45197</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45211</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>44872</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45238</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45167</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45704</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44656</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45161</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45694</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>46260</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45238</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45433</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>46260</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>46260</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>46099</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45237</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>44651</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45211</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45226</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45775</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46266</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45315</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46266</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46266</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>44830</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45302</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>46226</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45237</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45301</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46274</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46273</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45532</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45301</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45275</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>46276</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45320</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45252</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>45547</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44838</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45623</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45534</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46286</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>46282</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>46286</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>45008</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44952</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>46282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>46272</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44935</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46248</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44929</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45261</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>46248</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>46248</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>46289</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44893</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45607</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45268</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44469</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45210</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45267</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45419</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44995</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45053</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45317</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45371</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45771</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45407</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45407</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45212</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45764</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45301</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45315</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45102</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>44866</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>44664</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44642</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>45228</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>45366</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45371</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45015</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45094</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45611</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>44935</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45341</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>45334</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45719</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45252</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45321</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>44964</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45001</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45755</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>45253</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>45747</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45350</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45694</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45694</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45646</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45315</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45223</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45412</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45725</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45448</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45573</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45644</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45414</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45646</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45791</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45611</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>45791</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>44558</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44882</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45139</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45063</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45173</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45152</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>45152</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45620</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45600</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45141</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45762</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45776</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45786</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45785</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45794</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45794</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45712</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45712</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45818</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45840</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45985</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45985</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45985</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>46073</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>46091</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>46091</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>46106</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46119</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>46125</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>44008</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>46095</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>45037</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45722</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45719</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45890</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>46085</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>45981</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45168</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>46001</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45768</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>46266</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45170</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45218</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45646</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>46091</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44862</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44876</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44749</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>44805</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44510</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44855</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44809</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44573</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44886</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44862</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44532</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44580</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44826</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44746</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44608</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44844</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44869</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44862</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44857</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44833</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44662</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44853</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44468</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>44789</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44533</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44565</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>44664</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44502</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44541</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>44624</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44700</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44816</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44798</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44789</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44861</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45198</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45669</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>45334</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45198</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45338</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44781</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44475</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45211</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45448</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>45446</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45454</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45253</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45365</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44883</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45881</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>46014</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>46017</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45244</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45160</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45455</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45733</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45733</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45546</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44475</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44951</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45884</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45646</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>45110</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>45548</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45726</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44972</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45460</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45727</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45534</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45903</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45905</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45660</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45910</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44896</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45029</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45706</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45001</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>46066</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>46066</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>46066</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>46070</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45127</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>46070</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45671</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>44590</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45320</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>45320</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>44942</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45209</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44944</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>46087</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45541</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45061</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45037</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45601</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>46097</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45698</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45946</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>46101</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45524</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>46101</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>46101</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45953</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45953</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45954</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45953</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45953</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46108</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45957</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45959</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45959</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>46125</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45593</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>46125</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45106</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45623</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45966</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>44509</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45967</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>44991</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45971</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45978</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45975</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45975</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45975</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>44970</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45679</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45981</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45981</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45986</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45685</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45879</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45098</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45989</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45634</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45247</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45985</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45993</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44991</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44820</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45067</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44501</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45748</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>46008</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>46010</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45785</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>46014</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46014</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45695</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>46014</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>44957</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45274</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45240</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45825</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44886</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45079</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>44866</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45015</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45111</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45267</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45066</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45427</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45832</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45833</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45252</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45086</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44839</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45833</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45833</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>46125</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45094</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45764</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>44826</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45094</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45839</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45104</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44510</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46164</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45118</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44505</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>46168</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45418</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>46165</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45371</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45267</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45329</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>44474</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45146</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45110</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44833</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45148</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45771</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45166</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45607</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45607</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45534</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45037</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45634</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45634</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45469</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45104</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>44476</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>46184</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45518</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45170</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45607</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46191</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45040</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45758</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45534</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>46191</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45355</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45411</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45632</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45632</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45054</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45067</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>44601</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45084</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44610</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>45281</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45204</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45371</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45407</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46251</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45163</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45170</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45201</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45197</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45211</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>44872</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45238</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45167</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45704</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44656</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45161</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45694</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>46260</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45238</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45433</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>46260</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>46260</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>46099</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45237</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>44651</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45211</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45226</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45775</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46266</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45315</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46266</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46266</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>44830</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45302</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>46226</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45237</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45301</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46274</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46273</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45532</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45301</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45275</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>46276</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45320</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45252</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>45547</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44838</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45623</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45534</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46286</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>46282</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>46286</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>45008</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44952</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>46282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>46272</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44935</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46248</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44929</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45261</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>46248</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>46248</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>46289</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>44893</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45607</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45268</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44469</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45210</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45267</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45419</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44995</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45053</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>45317</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45371</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>45771</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         <v>45407</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45407</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45212</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45764</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45301</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45315</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45102</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>44866</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>44664</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44642</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>45228</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         <v>45366</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45371</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45015</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45094</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45611</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>44935</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45341</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>45334</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45719</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45252</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45321</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>44964</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45001</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45755</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28084,7 +28084,7 @@
         <v>45253</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>45747</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45350</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45694</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45694</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45646</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45315</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45223</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28668,7 +28668,7 @@
         <v>45412</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45725</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45448</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45573</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45644</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45414</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45646</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45791</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45611</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>45791</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>44558</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44882</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45139</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45063</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45173</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45152</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>45152</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45620</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45600</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45141</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45762</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45776</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45786</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45785</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45794</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45794</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45712</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45712</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45818</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45840</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>45985</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45985</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45985</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>46073</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>46091</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>46091</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>46106</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46119</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>46125</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>44008</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45999</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45037</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46095</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45890</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45719</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45168</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45722</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>46085</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45845</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>46001</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45646</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45351</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45530</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>45768</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>46266</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>46091</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44862</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44876</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44749</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>44510</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44809</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44573</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44886</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44862</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44532</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44580</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44826</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44746</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44608</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44844</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44869</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44862</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44857</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44833</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44662</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44853</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44790</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>44789</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44533</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44664</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44502</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44541</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44700</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>44624</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44861</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45775</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44789</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45698</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44664</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45094</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45086</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44952</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45725</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45252</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45412</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45212</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45460</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>45037</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45320</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45320</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45201</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45764</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>46008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>46010</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45791</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>46014</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>46014</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>46014</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46014</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45611</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45726</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>46017</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45350</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>44988</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45098</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45791</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45198</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45905</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45534</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45646</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>45706</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>45910</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44476</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>45518</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>45646</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45634</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>45634</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>45733</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45733</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45548</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45727</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45094</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45455</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45321</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45001</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45040</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>46066</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>46066</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>46066</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>46070</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46070</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45946</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44781</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>45067</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>45953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45957</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45953</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45953</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45237</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45959</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>46087</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45964</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45267</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44509</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45966</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45967</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>46097</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45971</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45671</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45228</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45167</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44995</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>46101</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45975</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45975</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>46101</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46101</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45975</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45671</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45978</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45679</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45981</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45371</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45981</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45102</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>46108</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45371</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45986</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>45547</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45302</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>44501</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>44838</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45989</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45825</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>44893</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45365</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44929</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45993</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>46125</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>46125</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44866</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44642</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45833</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45226</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45252</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45833</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45832</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45833</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45524</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45764</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45785</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45839</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44991</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45211</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45985</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45634</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45879</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45433</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45534</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45053</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45418</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>44991</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45593</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45315</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45001</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45247</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45315</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44820</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45110</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45015</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44474</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45419</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45329</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44833</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>44935</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45320</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45054</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45694</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44935</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44951</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45166</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45747</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44970</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>44957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44866</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45771</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45338</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45170</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45632</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45632</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45534</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>46125</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44886</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45209</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45197</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>44656</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>45407</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45407</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>45301</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45607</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>44826</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46164</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>46165</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45315</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>46168</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44505</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45446</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45719</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45881</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45407</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45669</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45110</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45884</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45607</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45226</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46184</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45067</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45240</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46191</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46191</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45771</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45546</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>45084</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45037</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45281</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45237</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45601</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44830</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>44806</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45469</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45534</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45163</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45161</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45660</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>46099</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45127</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>46260</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>46260</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44475</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>46260</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45411</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44510</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45268</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45341</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>46266</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45355</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>46266</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45252</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>46266</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>46226</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>46273</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45161</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45541</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45079</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45061</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>46274</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46276</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45748</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45238</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45244</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45211</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>45301</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45274</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>44872</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45008</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45104</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45170</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>46272</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>46286</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>44590</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>46282</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>46282</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>46286</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45623</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45611</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>44896</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45238</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44972</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45146</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45454</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45601</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45253</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45111</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>46248</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>46289</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45029</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45148</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46248</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45160</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>46248</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>44942</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>46293</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>46293</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45334</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45267</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>44944</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45427</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>44651</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>46295</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>46251</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>44964</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45210</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45094</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45694</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45694</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>46282</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45695</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>46294</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>44839</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45623</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45704</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>46296</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45317</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45371</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45371</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44830</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45275</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44883</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45261</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>44475</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45301</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45532</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45015</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45758</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45334</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45118</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45685</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45607</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45066</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45448</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45607</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45366</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45198</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45267</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45211</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45104</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45223</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45414</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45644</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45573</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45448</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45646</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44882</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45139</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45063</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45063</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45173</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45152</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>44558</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45152</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45620</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45600</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45141</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45762</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45776</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45786</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45785</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45794</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45794</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45712</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45712</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45818</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45985</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45985</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>46073</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46091</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>46091</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>46106</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>46119</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>46125</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>44008</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45999</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>45037</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>46095</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45890</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>45719</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>45168</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>45722</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>46085</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45845</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>46001</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45646</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45351</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45530</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>45768</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>46266</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>46091</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44862</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44876</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44749</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>44510</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44855</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44805</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44809</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44573</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44886</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44862</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44532</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44580</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44826</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44746</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44608</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44844</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44869</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44862</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44857</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>44833</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44662</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44853</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>44791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44790</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>44789</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44533</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44565</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44664</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44502</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>44541</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>44700</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>44624</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44816</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44861</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45775</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44789</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45698</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44664</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45094</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45086</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44952</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45725</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45252</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45412</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45212</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45460</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>45037</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45320</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45320</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45201</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45764</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>46008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>46010</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45791</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>46014</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>46014</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>46014</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46014</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45611</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45726</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>46017</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45350</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>44988</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45098</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45791</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45903</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45198</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45905</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45534</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45646</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>45706</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>45910</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44476</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>45518</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>45646</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>45106</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45634</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>45634</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>45733</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45733</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45548</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45727</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45094</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45455</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>45321</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45001</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45040</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>46066</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>46066</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>46066</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>46070</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46070</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45946</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44781</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>45067</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>45953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45957</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45953</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45953</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45237</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45959</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>46087</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45964</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45267</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44509</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45966</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45967</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>46097</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45971</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45671</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45228</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45167</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44995</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>46101</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45975</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45975</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>46101</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46101</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45975</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45671</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45978</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45679</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45981</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45371</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45981</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45102</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>46108</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45371</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45986</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>45547</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45302</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>44501</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>44838</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45989</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45825</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>44893</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45365</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44929</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45993</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>46125</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>46125</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44866</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44642</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45833</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45226</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45252</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45833</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45832</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45833</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45524</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>45764</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45785</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45839</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44991</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45211</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45985</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45634</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45879</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45433</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45534</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45053</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45418</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>44991</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45593</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45315</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45001</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45247</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45315</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44820</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45110</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45015</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44474</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45419</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45329</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44833</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>44935</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45320</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45054</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45694</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44935</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>44951</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45166</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45747</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44970</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>44957</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44866</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>45771</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45338</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45170</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45632</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45632</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45534</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>46125</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44886</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45209</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45197</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>44656</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>45407</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45407</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>45301</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45607</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>44826</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46164</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>46165</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45315</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>46168</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44505</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45446</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45719</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45881</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45407</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45669</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45110</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45884</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45607</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45226</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46184</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45067</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45240</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46191</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46191</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45771</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45546</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44601</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45755</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>45084</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45037</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45281</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45237</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45601</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44830</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>44806</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45469</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45534</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45163</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45161</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45660</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>46099</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45127</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>46260</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>46260</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44475</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>46260</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45411</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44510</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45268</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45341</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>46266</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45355</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>46266</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45252</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>46266</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>46226</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>46273</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45161</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45541</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45079</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45061</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>46274</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46276</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45748</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45238</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45244</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45211</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>45301</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45274</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>44872</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45008</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45104</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45170</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>46272</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>46286</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>44590</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>46282</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>46282</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>46286</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45623</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45611</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>44896</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45238</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44972</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45146</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45454</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45601</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45253</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45111</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>46248</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>46289</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45029</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45148</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46248</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45160</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>46248</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>44942</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>46293</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>46293</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45334</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45267</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>44944</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>45427</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>44651</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>46295</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>46251</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>44964</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>45210</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45094</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45694</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45694</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>46282</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45695</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>46294</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>44839</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45623</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45704</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>46296</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45317</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45371</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45371</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44830</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45275</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44883</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45261</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>44475</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45301</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45532</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45015</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45758</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28386,7 +28386,7 @@
         <v>45334</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45118</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45685</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45607</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45066</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45448</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
         <v>45607</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45366</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45198</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>45267</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45211</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45104</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45223</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45414</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45644</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45573</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45448</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45646</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44882</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45139</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45063</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45063</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45173</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>45152</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>44558</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45152</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45620</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45600</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45141</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45762</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45776</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45786</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45785</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45794</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45794</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45712</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45712</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45818</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45985</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45985</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>46073</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>46091</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>46091</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>46106</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>46119</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>46125</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>44008</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>46302</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45037</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>46095</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45646</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45890</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>45722</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>45719</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45168</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45768</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45170</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45218</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45351</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45845</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>46001</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>46085</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>46266</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>46300</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>46300</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>46091</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>44862</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44876</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>44533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44749</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>44805</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44510</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>44855</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>44809</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>44573</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>44603</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44862</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>44886</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44862</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44532</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44572</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44580</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44826</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44746</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44502</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44541</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44533</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44624</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44608</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>44700</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44518</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44565</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44844</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44833</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44852</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44662</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44664</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>44853</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44791</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44857</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44862</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45066</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44798</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44789</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>45427</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44861</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>45211</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>45053</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>45317</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>45371</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45252</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44839</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45448</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45446</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45198</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45669</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45334</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45198</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45771</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45407</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45407</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>45094</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44826</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45094</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45338</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45212</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45764</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45104</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44781</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45301</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45315</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45454</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44510</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45102</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45253</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44866</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44664</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45365</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44642</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45118</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45228</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44505</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45366</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>45371</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45267</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45371</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45881</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44883</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45015</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45094</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45611</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>44935</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45244</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45884</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45341</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45110</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45226</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45146</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>45160</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45726</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>45460</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45148</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45455</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45334</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45771</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>45719</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45252</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45166</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>45546</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>44951</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45321</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44964</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>45001</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>45755</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45253</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45747</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45350</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45694</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>45694</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45607</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>45607</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>45646</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>45903</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>45534</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>45315</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45905</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45910</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45037</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45534</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45634</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>45634</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45469</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45104</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44988</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45706</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>45223</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45660</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44896</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45412</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45029</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45725</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45448</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45573</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45518</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45644</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45414</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45170</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45607</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45040</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45758</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45534</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45646</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45127</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45355</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45411</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45671</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44590</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45632</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45632</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>45611</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45791</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45320</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45320</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45054</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45067</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>44942</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45209</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>44601</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45733</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45733</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44944</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45541</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45084</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>44610</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45061</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45037</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45646</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45548</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45601</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45281</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45727</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45204</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45371</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45601</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45407</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45163</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45170</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45698</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45201</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45197</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45211</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45946</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44872</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45238</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45167</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45704</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>44656</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45694</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45825</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45593</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45106</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45623</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45238</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45433</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44509</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>44991</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45832</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45671</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45953</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45953</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45954</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45953</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45953</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45957</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45959</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45959</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45833</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45833</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45833</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45237</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45764</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45964</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44651</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44970</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45679</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45839</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45966</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45211</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45967</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45226</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45971</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45685</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45098</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45775</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45315</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45418</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45634</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45978</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45329</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44830</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45110</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45302</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44833</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44991</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45975</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45975</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45975</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44820</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45067</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45237</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44501</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45301</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45748</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45695</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45981</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45274</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45532</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45240</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45301</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45275</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44886</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45320</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45986</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45252</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>46101</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>46101</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>46101</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>45986</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45079</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>44866</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45015</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45547</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44838</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45111</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45623</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46108</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45989</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45267</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45534</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45993</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>46125</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>46125</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45008</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44952</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44935</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45879</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>46008</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>44929</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45261</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>46010</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45247</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>46014</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>46014</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>46014</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>46014</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>46017</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44893</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45607</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45785</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>45268</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44957</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45210</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45267</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45419</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44995</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>46066</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>46066</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>46066</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>46070</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46070</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>46125</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>46087</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>46097</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>46164</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>46168</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>46165</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>46191</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46191</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>46099</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>46266</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>46266</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>46266</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>46226</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>46274</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>46276</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>46286</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>46286</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46282</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>46282</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46272</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>46293</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>46293</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>46251</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>46294</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>46295</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>46296</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>46294</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>46184</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45981</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>46301</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>46248</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>46273</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>46282</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>46289</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>46303</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>46248</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>46248</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>46260</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>46260</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>44558</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44882</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45139</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45063</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45063</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45173</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45152</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45152</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45620</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45600</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45141</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45762</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45776</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45786</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45785</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45794</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45794</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>45712</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45712</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45818</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45985</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45985</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>46073</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>46091</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>46091</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>46106</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>46119</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>46125</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>44008</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>45999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>46302</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>45037</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>46095</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45646</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45890</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>45722</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>45719</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>45168</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>45981</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45768</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45170</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45218</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45351</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45845</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>46001</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45530</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>46085</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>46266</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>46300</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>46300</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>46091</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>44862</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44876</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>44533</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44749</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>44805</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>44510</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>44855</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>44809</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>44573</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>44603</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44862</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>44886</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44862</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44532</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44572</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44580</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44826</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44746</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44502</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44541</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44790</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44533</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44624</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44608</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>44700</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44518</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44565</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44844</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44833</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44852</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44662</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44664</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>44853</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44791</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44857</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44862</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45066</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44798</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44789</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>45427</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44861</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>45211</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>45053</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>45317</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>45371</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45252</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44839</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45448</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45446</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45198</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45669</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45334</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45198</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45771</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45407</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45407</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>45094</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44826</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45094</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45338</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45212</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45764</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45104</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44781</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45301</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45315</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45454</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44510</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45102</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45253</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44866</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44664</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45365</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44642</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45118</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45228</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44505</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45366</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>45371</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45267</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45371</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45881</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44883</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45015</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45094</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45611</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>44935</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45244</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45884</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45341</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45110</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45226</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45146</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>45160</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45726</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>45460</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45148</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45455</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45334</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45771</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>45719</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45252</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45166</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>45546</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>44951</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45321</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44964</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>45001</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>45755</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>45253</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45747</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>45350</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45694</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>45694</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45607</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>45607</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>45646</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>45903</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>45534</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>45315</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45905</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45910</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45037</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45534</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45634</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>45634</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>45469</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45104</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44988</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45706</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>45223</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45660</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44896</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45412</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45029</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45725</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45448</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45573</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45518</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45644</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45414</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45170</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45607</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45040</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45758</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45534</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>45646</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45127</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45355</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45411</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45671</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44590</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45632</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45632</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>45611</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45791</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45320</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45320</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45054</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45067</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>44942</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45209</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>44601</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45733</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45733</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44944</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45541</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45084</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>44610</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45061</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45037</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45646</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45548</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45601</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45281</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45727</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45204</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45371</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45601</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45407</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45163</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45170</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45698</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45201</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45197</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45524</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45211</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45946</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44872</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45238</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45167</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45704</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>44656</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45694</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45825</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45593</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45106</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45623</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45238</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45433</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44509</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>44991</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45832</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45671</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45953</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45953</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45954</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45953</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45953</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45957</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45959</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45959</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45833</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45833</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45833</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45237</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45764</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45964</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44651</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44970</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45679</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45839</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45966</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45211</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45967</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45226</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45971</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45685</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45098</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45775</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45315</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45418</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45634</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45978</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45329</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44830</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45110</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45302</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44833</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44991</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45975</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45975</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45975</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44820</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45067</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45237</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44501</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45301</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45748</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45695</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45981</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45274</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45532</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45240</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45301</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45275</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44886</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45320</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45986</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45252</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>46101</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>46101</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>46101</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>45986</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45079</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>44866</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45015</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45547</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44838</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45111</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45623</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46108</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45989</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45267</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45534</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45993</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>46125</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>46125</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45008</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44952</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44935</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45879</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>46008</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>44929</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45261</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>46010</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45247</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>46014</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>46014</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>46014</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>46014</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>46017</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44893</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45607</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45785</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>45268</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44957</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45210</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45267</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45419</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44995</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>46066</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>46066</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>46066</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>46070</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46070</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>46125</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>46087</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>46097</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>46164</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>46168</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>46165</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>46191</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46191</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>46099</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>46266</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>46266</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>46266</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>46226</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>46274</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>46276</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>46286</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>46286</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46282</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>46282</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46272</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>46293</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>46293</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>46251</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>46294</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>46295</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>46296</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>46294</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>46184</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45981</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>46301</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>46248</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>46273</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>46282</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>46289</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>46303</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>46248</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>46248</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>46260</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>46260</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>44558</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44882</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>45139</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45063</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45063</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45173</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45152</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45152</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45620</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45600</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45141</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45762</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45776</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45786</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45785</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45794</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45794</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>45712</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45712</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45818</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45985</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45985</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>46073</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>46091</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>46091</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>46106</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>46119</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>46125</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>46309</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44008</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>44847</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45217</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>46302</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45037</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>46095</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45168</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>45890</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>46001</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45646</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>45981</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45351</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45530</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>45768</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>46085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>46300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>46300</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45719</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45722</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>46266</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>46091</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44862</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>44876</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44533</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44749</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>44510</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44805</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44855</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>44809</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44573</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>44603</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>44862</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44886</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>44862</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>44532</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44572</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44580</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>44746</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44608</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44844</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>44852</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44869</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44857</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44862</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44582</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44518</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44833</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44662</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>44853</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44791</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44790</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44533</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44565</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44664</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44502</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44541</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44624</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44700</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44816</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44798</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44789</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44861</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45775</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>45698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45094</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45086</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>44664</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45252</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44952</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45212</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45037</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45320</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>45320</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>45201</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>45764</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44988</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>45350</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>45198</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>45534</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>45098</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>45518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>45646</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45106</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>45634</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>45634</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45455</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45321</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45094</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>45040</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>44781</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>45067</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45001</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45237</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45267</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44509</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45228</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45671</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45167</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44995</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45671</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>45371</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>45679</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45102</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>45371</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45879</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>45547</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>45302</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>44501</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44838</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>44893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45365</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>44929</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44866</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45110</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45884</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44642</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>45726</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>45460</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45247</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45226</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>45252</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45524</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>45903</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>45905</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44991</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44957</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>45706</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>45211</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>45634</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>45433</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>45534</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>45053</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44991</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45593</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45315</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45001</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>45315</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44820</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>45015</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>45419</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45946</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44935</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>45320</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>46125</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>45054</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45953</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>45694</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>45953</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45957</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45953</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45953</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>45954</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>44935</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>45959</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45959</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>44951</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>45166</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>45966</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45747</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44970</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>45971</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>44866</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>45975</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45975</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>45975</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45771</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45338</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45978</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45170</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45632</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>45632</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45981</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45534</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44886</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>46164</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>46165</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45986</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45986</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45989</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45204</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45197</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45993</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>46168</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>44656</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45407</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45407</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45301</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45607</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>44826</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45315</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>44505</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45446</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>46008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45719</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>46010</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>45407</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45669</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>46014</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>46014</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>46014</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>46014</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45607</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>46017</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45226</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>45067</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45240</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45771</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45546</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44601</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45755</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>45084</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>45037</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>45281</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>46066</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>46066</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>46066</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>45237</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45601</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>46070</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>46070</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44830</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44806</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45469</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45534</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45163</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>46087</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>46191</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>46191</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>45161</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45660</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>46097</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45127</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>46101</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>46101</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>46101</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45411</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45253</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44510</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>46108</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45268</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45341</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45355</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45252</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>46125</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>46125</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45161</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45541</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45079</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45061</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45785</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45748</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45238</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45211</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45985</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45301</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45274</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44872</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45008</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45104</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45170</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>46099</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44590</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45623</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45611</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>44896</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45238</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44972</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>46226</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45146</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45454</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>45601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45253</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>45111</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>46274</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45029</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45148</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45160</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>44942</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>46276</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45334</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45267</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>44944</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45427</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>44651</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>44964</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>45094</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>45694</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45694</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>45695</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>44839</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>45623</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45704</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45317</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>46272</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45371</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45371</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44830</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>46286</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45275</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>44883</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45261</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>46282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>46282</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>46286</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>45301</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>45532</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>45015</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45758</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45334</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45118</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45685</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45607</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45066</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45448</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45607</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>46293</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>46293</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>46294</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45366</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>46295</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>46251</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>46294</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45267</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45211</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>46296</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45981</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>46301</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45223</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45414</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45644</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45573</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45448</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>46184</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45646</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45725</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45412</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>46260</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>46260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>46303</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45791</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45611</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45791</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45646</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>46289</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46273</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>45733</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45733</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45548</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45727</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>46248</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46248</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>46308</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>46266</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>46266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>46308</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>46266</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>46248</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>46308</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45825</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>46282</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45833</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>45833</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45832</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45833</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45764</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45839</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45418</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>45110</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>45329</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>44833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>44882</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45139</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45063</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>45063</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>45173</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>45152</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>44558</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>45152</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>45620</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>45600</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>45141</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>45762</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>45776</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>45786</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>45785</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>45794</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45794</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>45712</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>45712</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45818</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45840</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>45985</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>45985</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45985</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>46073</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>46091</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>46091</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>46106</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>46119</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46125</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>46309</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44008</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>44847</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45217</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>46302</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45037</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>46095</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45168</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45845</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>45890</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>46001</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61482-2024</t>
+          <t>A 18174-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2208,14 +2208,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45646</v>
+        <v>46125</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2252,10 +2252,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2264,1383 +2264,1419 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 18174-2026 artfynd.xlsx", "A 18174-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 18174-2026 karta.png", "A 18174-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 18174-2026 georefererad karta.tif", "A 18174-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 18174-2026 FSC-klagomål.docx", "A 18174-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 18174-2026 FSC-klagomål mail.docx", "A 18174-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 18174-2026 tillsynsbegäran.docx", "A 18174-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 18174-2026 tillsynsbegäran mail.docx", "A 18174-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0684/fåglar/A 18174-2026 prioriterade fågelarter.docx", "A 18174-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 61482-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45646</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 61482-2024 artfynd.xlsx", "A 61482-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 61482-2024 karta.png", "A 61482-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 61482-2024 georefererad karta.tif", "A 61482-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 61482-2024 FSC-klagomål.docx", "A 61482-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 61482-2024 FSC-klagomål mail.docx", "A 61482-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 61482-2024 tillsynsbegäran.docx", "A 61482-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 61482-2024 tillsynsbegäran mail.docx", "A 61482-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 57846-2025</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45981</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>2.1</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 57846-2025 artfynd.xlsx", "A 57846-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 57846-2025 karta.png", "A 57846-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 57846-2025 georefererad karta.tif", "A 57846-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 57846-2025 FSC-klagomål.docx", "A 57846-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 57846-2025 FSC-klagomål mail.docx", "A 57846-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 57846-2025 tillsynsbegäran.docx", "A 57846-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 57846-2025 tillsynsbegäran mail.docx", "A 57846-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 8198-2024</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>45351</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.7</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Småfruktigt blågryn</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 8198-2024 artfynd.xlsx", "A 8198-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 8198-2024 karta.png", "A 8198-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 8198-2024 georefererad karta.tif", "A 8198-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 8198-2024 FSC-klagomål.docx", "A 8198-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 8198-2024 FSC-klagomål mail.docx", "A 8198-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 8198-2024 tillsynsbegäran.docx", "A 8198-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 8198-2024 tillsynsbegäran mail.docx", "A 8198-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 35136-2024</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>45530</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>2.1</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 35136-2024 artfynd.xlsx", "A 35136-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 35136-2024 karta.png", "A 35136-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 35136-2024 georefererad karta.tif", "A 35136-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 35136-2024 FSC-klagomål.docx", "A 35136-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 35136-2024 FSC-klagomål mail.docx", "A 35136-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 35136-2024 tillsynsbegäran.docx", "A 35136-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 35136-2024 tillsynsbegäran mail.docx", "A 35136-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 19123-2025</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>45768</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>0.6</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 19123-2025 artfynd.xlsx", "A 19123-2025")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 19123-2025 karta.png", "A 19123-2025")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 19123-2025 georefererad karta.tif", "A 19123-2025")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 19123-2025 FSC-klagomål.docx", "A 19123-2025")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 19123-2025 FSC-klagomål mail.docx", "A 19123-2025")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 19123-2025 tillsynsbegäran.docx", "A 19123-2025")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 19123-2025 tillsynsbegäran mail.docx", "A 19123-2025")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/fåglar/A 19123-2025 prioriterade fågelarter.docx", "A 19123-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 11797-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>46085</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>2.7</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 11797-2026 artfynd.xlsx", "A 11797-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 11797-2026 karta.png", "A 11797-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 11797-2026 georefererad karta.tif", "A 11797-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 11797-2026 FSC-klagomål.docx", "A 11797-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 11797-2026 FSC-klagomål mail.docx", "A 11797-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 11797-2026 tillsynsbegäran.docx", "A 11797-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 11797-2026 tillsynsbegäran mail.docx", "A 11797-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 51095-2023</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>45218</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>3.6</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Korallrot</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 51095-2023 artfynd.xlsx", "A 51095-2023")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 51095-2023 karta.png", "A 51095-2023")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 51095-2023 georefererad karta.tif", "A 51095-2023")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 51095-2023 FSC-klagomål.docx", "A 51095-2023")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 51095-2023 FSC-klagomål mail.docx", "A 51095-2023")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 51095-2023 tillsynsbegäran.docx", "A 51095-2023")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 51095-2023 tillsynsbegäran mail.docx", "A 51095-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 41170-2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46300</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>0.7</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 41170-2026 artfynd.xlsx", "A 41170-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 41170-2026 karta.png", "A 41170-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 41170-2026 georefererad karta.tif", "A 41170-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 41170-2026 FSC-klagomål.docx", "A 41170-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 41170-2026 FSC-klagomål mail.docx", "A 41170-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 41170-2026 tillsynsbegäran.docx", "A 41170-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 41170-2026 tillsynsbegäran mail.docx", "A 41170-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 41179-2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>46300</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>8.6</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 41179-2026 artfynd.xlsx", "A 41179-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 41179-2026 karta.png", "A 41179-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 41179-2026 georefererad karta.tif", "A 41179-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 41179-2026 FSC-klagomål.docx", "A 41179-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 41179-2026 FSC-klagomål mail.docx", "A 41179-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 41179-2026 tillsynsbegäran.docx", "A 41179-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 41179-2026 tillsynsbegäran mail.docx", "A 41179-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 10046-2025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>45719</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+      <c r="E27" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>8.6</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 10046-2025 artfynd.xlsx", "A 10046-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 10046-2025 karta.png", "A 10046-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 10046-2025 georefererad karta.tif", "A 10046-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 10046-2025 FSC-klagomål.docx", "A 10046-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 10046-2025 FSC-klagomål mail.docx", "A 10046-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 10046-2025 tillsynsbegäran.docx", "A 10046-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 10046-2025 tillsynsbegäran mail.docx", "A 10046-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 10775-2025</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D28" s="1" t="n">
         <v>45722</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E28" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>10.1</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>1</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T28" t="n">
         <v>1</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>1</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Solvända</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 10775-2025 artfynd.xlsx", "A 10775-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 10775-2025 karta.png", "A 10775-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 10775-2025 georefererad karta.tif", "A 10775-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 10775-2025 FSC-klagomål.docx", "A 10775-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 10775-2025 FSC-klagomål mail.docx", "A 10775-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 10775-2025 tillsynsbegäran.docx", "A 10775-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 10775-2025 tillsynsbegäran mail.docx", "A 10775-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 35891-2026</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+      <c r="E29" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>2.2</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S29" t="n">
         <v>1</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>1</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Pilfibbla</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/A 35891-2026 artfynd.xlsx", "A 35891-2026")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/A 35891-2026 karta.png", "A 35891-2026")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/A 35891-2026 georefererad karta.tif", "A 35891-2026")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/A 35891-2026 FSC-klagomål.docx", "A 35891-2026")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/A 35891-2026 FSC-klagomål mail.docx", "A 35891-2026")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/A 35891-2026 tillsynsbegäran.docx", "A 35891-2026")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/A 35891-2026 tillsynsbegäran mail.docx", "A 35891-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>S 689-2026</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>46091</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SÄVSJÖ</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>21.4</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Igelkott</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/artfynd/S 689-2026 artfynd.xlsx", "S 689-2026")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor/S 689-2026 karta.png", "S 689-2026")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/kartor_geotiff/S 689-2026 georefererad karta.tif", "S 689-2026")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomål/S 689-2026 FSC-klagomål.docx", "S 689-2026")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/klagomålsmail/S 689-2026 FSC-klagomål mail.docx", "S 689-2026")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsyn/S 689-2026 tillsynsbegäran.docx", "S 689-2026")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0684/tillsynsmail/S 689-2026 tillsynsbegäran mail.docx", "S 689-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 49668-2022</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>44862</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>SÄVSJÖ</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr"/>
-    </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53099-2022</t>
+          <t>A 49668-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,10 +3690,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44876</v>
+        <v>44862</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3670,7 +3706,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3713,7 +3749,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 69990-2021</t>
+          <t>A 53099-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3727,10 +3763,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44533</v>
+        <v>44876</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3743,7 +3779,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3786,7 +3822,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28908-2022</t>
+          <t>A 69990-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3800,10 +3836,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44749</v>
+        <v>44533</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3816,7 +3852,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3859,7 +3895,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64021-2021</t>
+          <t>A 28908-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3873,10 +3909,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44510</v>
+        <v>44749</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3889,7 +3925,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3932,7 +3968,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36778-2022</t>
+          <t>A 64021-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3946,10 +3982,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44805</v>
+        <v>44510</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3962,7 +3998,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4005,7 +4041,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47957-2022</t>
+          <t>A 36778-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4015,14 +4051,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44855</v>
+        <v>44805</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4034,13 +4070,8 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4083,7 +4114,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37323-2022</t>
+          <t>A 47957-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4093,14 +4124,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44809</v>
+        <v>44855</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4112,8 +4143,13 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4156,7 +4192,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1391-2022</t>
+          <t>A 37323-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4170,10 +4206,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44573</v>
+        <v>44809</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4186,7 +4222,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4229,7 +4265,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7115-2022</t>
+          <t>A 1391-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4243,10 +4279,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44603</v>
+        <v>44573</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4259,7 +4295,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4302,7 +4338,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49662-2022</t>
+          <t>A 7115-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4316,10 +4352,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44862</v>
+        <v>44603</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4332,7 +4368,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4375,7 +4411,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55136-2022</t>
+          <t>A 49662-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4389,10 +4425,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44886</v>
+        <v>44862</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4405,7 +4441,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4448,7 +4484,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 49653-2022</t>
+          <t>A 55136-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4462,10 +4498,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44862</v>
+        <v>44886</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4478,7 +4514,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4521,7 +4557,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 69638-2021</t>
+          <t>A 49653-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4535,10 +4571,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44532</v>
+        <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4551,7 +4587,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4594,7 +4630,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1307-2022</t>
+          <t>A 69638-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4608,10 +4644,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44572</v>
+        <v>44532</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4624,7 +4660,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4667,7 +4703,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2654-2022</t>
+          <t>A 1307-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4681,10 +4717,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44580</v>
+        <v>44572</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4697,7 +4733,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4740,7 +4776,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 41210-2022</t>
+          <t>A 2654-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4754,10 +4790,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44826</v>
+        <v>44580</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4770,7 +4806,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4813,7 +4849,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 28127-2022</t>
+          <t>A 41210-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4827,10 +4863,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44746</v>
+        <v>44826</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4843,7 +4879,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4886,7 +4922,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7762-2022</t>
+          <t>A 28127-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4896,14 +4932,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44608</v>
+        <v>44746</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4916,7 +4952,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4959,7 +4995,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45155-2022</t>
+          <t>A 7762-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4969,14 +5005,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44844</v>
+        <v>44608</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4988,13 +5024,8 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5037,7 +5068,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47095-2022</t>
+          <t>A 45155-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5047,14 +5078,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44852</v>
+        <v>44844</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5066,8 +5097,13 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5110,7 +5146,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51374-2022</t>
+          <t>A 47095-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5124,10 +5160,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44869</v>
+        <v>44852</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5140,7 +5176,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5183,7 +5219,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 48124-2022</t>
+          <t>A 51374-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5197,10 +5233,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44857</v>
+        <v>44869</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5213,7 +5249,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5256,7 +5292,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 49660-2022</t>
+          <t>A 48124-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5270,10 +5306,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44862</v>
+        <v>44857</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5286,7 +5322,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5329,7 +5365,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3131-2022</t>
+          <t>A 49660-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5343,10 +5379,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44582</v>
+        <v>44862</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5359,7 +5395,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5402,7 +5438,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54584-2022</t>
+          <t>A 3131-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5416,10 +5452,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44883</v>
+        <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5432,7 +5468,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5475,7 +5511,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 66396-2021</t>
+          <t>A 54584-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5485,14 +5521,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44518</v>
+        <v>44883</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5505,7 +5541,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5548,7 +5584,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42992-2022</t>
+          <t>A 66396-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5558,14 +5594,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44833</v>
+        <v>44518</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5578,7 +5614,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5621,7 +5657,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15670-2022</t>
+          <t>A 42992-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5635,10 +5671,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44662</v>
+        <v>44833</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5651,7 +5687,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5694,7 +5730,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47542-2022</t>
+          <t>A 15670-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5708,10 +5744,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44853</v>
+        <v>44662</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5724,7 +5760,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5767,7 +5803,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34119-2022</t>
+          <t>A 47542-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5781,10 +5817,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44791</v>
+        <v>44853</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5797,7 +5833,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5840,7 +5876,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33560-2022</t>
+          <t>A 34119-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5854,10 +5890,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44789</v>
+        <v>44791</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5870,7 +5906,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5913,7 +5949,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33938-2022</t>
+          <t>A 33560-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5927,10 +5963,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44790</v>
+        <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5943,7 +5979,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5986,7 +6022,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 69927-2021</t>
+          <t>A 33938-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6000,10 +6036,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44533</v>
+        <v>44790</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6016,7 +6052,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6059,7 +6095,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 363-2022</t>
+          <t>A 69927-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6073,10 +6109,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44565</v>
+        <v>44533</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6089,7 +6125,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6132,7 +6168,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15816-2022</t>
+          <t>A 363-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6146,10 +6182,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44664</v>
+        <v>44565</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6161,13 +6197,8 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6210,7 +6241,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 61944-2021</t>
+          <t>A 15816-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6224,10 +6255,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44502</v>
+        <v>44664</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6239,8 +6270,13 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6283,7 +6319,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 71610-2021</t>
+          <t>A 61944-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6297,10 +6333,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44541</v>
+        <v>44502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6313,7 +6349,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6356,7 +6392,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10592-2022</t>
+          <t>A 71610-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6370,10 +6406,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44624</v>
+        <v>44541</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6386,7 +6422,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6429,7 +6465,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20603-2022</t>
+          <t>A 10592-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6439,14 +6475,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44700</v>
+        <v>44624</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6459,7 +6495,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6502,7 +6538,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38950-2022</t>
+          <t>A 20603-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6512,14 +6548,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44816</v>
+        <v>44700</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6532,7 +6568,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6575,7 +6611,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35446-2022</t>
+          <t>A 38950-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6589,10 +6625,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44798</v>
+        <v>44816</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6648,7 +6684,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 33556-2022</t>
+          <t>A 35446-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6662,10 +6698,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44789</v>
+        <v>44798</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6678,7 +6714,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6721,7 +6757,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49221-2022</t>
+          <t>A 33556-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6735,10 +6771,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44861</v>
+        <v>44789</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6751,7 +6787,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6794,7 +6830,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20576-2025</t>
+          <t>A 49221-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6808,10 +6844,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45775</v>
+        <v>44861</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6824,7 +6860,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6867,7 +6903,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8341-2022</t>
+          <t>A 20576-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6881,10 +6917,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44610</v>
+        <v>45775</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6897,7 +6933,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6940,7 +6976,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6333-2025</t>
+          <t>A 8341-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6954,10 +6990,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45698</v>
+        <v>44610</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6970,7 +7006,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7013,7 +7049,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27013-2023</t>
+          <t>A 6333-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7027,10 +7063,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45094</v>
+        <v>45698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7043,7 +7079,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7086,7 +7122,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25118-2023</t>
+          <t>A 27013-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7100,10 +7136,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45086</v>
+        <v>45094</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7116,7 +7152,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7159,7 +7195,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 15834-2022</t>
+          <t>A 25118-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7173,10 +7209,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44664</v>
+        <v>45086</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7189,7 +7225,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7232,7 +7268,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59057-2023</t>
+          <t>A 15834-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7246,10 +7282,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45252</v>
+        <v>44664</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7262,7 +7298,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7305,7 +7341,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4030-2023</t>
+          <t>A 59057-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7319,10 +7355,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44952</v>
+        <v>45252</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7335,7 +7371,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7378,7 +7414,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49708-2023</t>
+          <t>A 4030-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7392,10 +7428,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45212</v>
+        <v>44952</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7408,7 +7444,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7451,7 +7487,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17766-2023</t>
+          <t>A 49708-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7465,10 +7501,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45037</v>
+        <v>45212</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7481,7 +7517,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7524,7 +7560,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3598-2024</t>
+          <t>A 17766-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7538,10 +7574,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45320</v>
+        <v>45037</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7554,7 +7590,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7597,7 +7633,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3600-2024</t>
+          <t>A 3598-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7614,7 +7650,7 @@
         <v>45320</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7627,7 +7663,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7670,7 +7706,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46906-2023</t>
+          <t>A 3600-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7684,10 +7720,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45201</v>
+        <v>45320</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7700,7 +7736,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7743,7 +7779,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19017-2025</t>
+          <t>A 46906-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7757,10 +7793,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45764</v>
+        <v>45201</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7773,7 +7809,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7816,7 +7852,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10591-2023</t>
+          <t>A 19017-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7830,10 +7866,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44988</v>
+        <v>45764</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7846,7 +7882,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7889,7 +7925,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7917-2024</t>
+          <t>A 10591-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7899,14 +7935,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45350</v>
+        <v>44988</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7919,7 +7955,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7962,7 +7998,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46580-2023</t>
+          <t>A 7917-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7972,14 +8008,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45198</v>
+        <v>45350</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7992,7 +8028,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8035,7 +8071,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36391-2024</t>
+          <t>A 46580-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8049,10 +8085,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45534</v>
+        <v>45198</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8065,7 +8101,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8108,7 +8144,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 27713-2023</t>
+          <t>A 36391-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8122,10 +8158,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45098</v>
+        <v>45534</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8138,7 +8174,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8181,7 +8217,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33154-2024</t>
+          <t>A 27713-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8195,10 +8231,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45518</v>
+        <v>45098</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8211,7 +8247,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8254,7 +8290,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61408-2024</t>
+          <t>A 33154-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8268,10 +8304,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45646</v>
+        <v>45518</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8284,7 +8320,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8327,7 +8363,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 29558-2023</t>
+          <t>A 61408-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8341,10 +8377,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45106</v>
+        <v>45646</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8357,7 +8393,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8400,7 +8436,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58397-2024</t>
+          <t>A 29558-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8414,10 +8450,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45634</v>
+        <v>45106</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8430,7 +8466,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8473,7 +8509,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 58398-2024</t>
+          <t>A 58397-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8490,7 +8526,7 @@
         <v>45634</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8503,7 +8539,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8546,7 +8582,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23885-2024</t>
+          <t>A 58398-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8560,10 +8596,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45455</v>
+        <v>45634</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8576,7 +8612,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8619,7 +8655,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 3662-2024</t>
+          <t>A 23885-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8633,10 +8669,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45321</v>
+        <v>45455</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8649,7 +8685,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8692,7 +8728,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27014-2023</t>
+          <t>A 3662-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8706,10 +8742,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45094</v>
+        <v>45321</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8722,7 +8758,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8765,7 +8801,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18135-2023</t>
+          <t>A 27014-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8779,10 +8815,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45040</v>
+        <v>45094</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8795,7 +8831,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8838,7 +8874,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32177-2022</t>
+          <t>A 18135-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8852,10 +8888,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44781</v>
+        <v>45040</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8868,7 +8904,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>6.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8911,7 +8947,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21801-2023</t>
+          <t>A 32177-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8925,10 +8961,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45067</v>
+        <v>44781</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8941,7 +8977,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8984,7 +9020,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 12952-2023</t>
+          <t>A 21801-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8998,10 +9034,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45001</v>
+        <v>45067</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9013,13 +9049,8 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9062,7 +9093,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55012-2023</t>
+          <t>A 12952-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9076,10 +9107,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45237</v>
+        <v>45001</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9091,8 +9122,13 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9135,7 +9171,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 62178-2023</t>
+          <t>A 55012-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9149,10 +9185,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45267</v>
+        <v>45237</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9165,7 +9201,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9208,7 +9244,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 63920-2021</t>
+          <t>A 62178-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9222,10 +9258,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44509</v>
+        <v>45267</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9238,7 +9274,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9281,7 +9317,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53102-2023</t>
+          <t>A 63920-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9295,10 +9331,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45228</v>
+        <v>44509</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9311,7 +9347,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9354,7 +9390,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1902-2025</t>
+          <t>A 53102-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9368,10 +9404,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45671</v>
+        <v>45228</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9384,7 +9420,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9427,7 +9463,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39730-2023</t>
+          <t>A 1902-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9441,10 +9477,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45167</v>
+        <v>45671</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9457,7 +9493,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9500,7 +9536,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11931-2023</t>
+          <t>A 39730-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9514,10 +9550,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44995</v>
+        <v>45167</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9530,7 +9566,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9573,7 +9609,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1916-2025</t>
+          <t>A 11931-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9587,10 +9623,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45671</v>
+        <v>44995</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9603,7 +9639,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9646,7 +9682,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 11239-2024</t>
+          <t>A 1916-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9660,10 +9696,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45371</v>
+        <v>45671</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9676,7 +9712,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9719,7 +9755,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3177-2025</t>
+          <t>A 11239-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9733,10 +9769,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45679</v>
+        <v>45371</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9749,7 +9785,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9792,7 +9828,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28423-2023</t>
+          <t>A 3177-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9806,10 +9842,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45102</v>
+        <v>45679</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9822,7 +9858,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9865,7 +9901,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 11266-2024</t>
+          <t>A 28423-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9879,10 +9915,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45371</v>
+        <v>45102</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9895,7 +9931,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9938,7 +9974,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 37545-2025</t>
+          <t>A 11266-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9952,10 +9988,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45879</v>
+        <v>45371</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9968,7 +10004,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10011,7 +10047,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 38914-2024</t>
+          <t>A 37545-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10021,14 +10057,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45547</v>
+        <v>45879</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10041,7 +10077,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10084,7 +10120,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1201-2024</t>
+          <t>A 38914-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10094,14 +10130,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45302</v>
+        <v>45547</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10114,7 +10150,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10157,7 +10193,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61545-2021</t>
+          <t>A 1201-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10171,10 +10207,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44501</v>
+        <v>45302</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10187,7 +10223,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10230,7 +10266,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 43976-2022</t>
+          <t>A 61545-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10244,10 +10280,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44838</v>
+        <v>44501</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10260,7 +10296,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10303,7 +10339,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56617-2022</t>
+          <t>A 43976-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10317,10 +10353,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44893</v>
+        <v>44838</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10333,7 +10369,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10376,7 +10412,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 10284-2024</t>
+          <t>A 56617-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10390,10 +10426,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45365</v>
+        <v>44893</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10406,7 +10442,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10449,7 +10485,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 297-2023</t>
+          <t>A 10284-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10463,10 +10499,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44929</v>
+        <v>45365</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10479,7 +10515,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10522,7 +10558,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 50627-2022</t>
+          <t>A 297-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10532,14 +10568,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44866</v>
+        <v>44929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10552,7 +10588,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10595,7 +10631,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30162-2023</t>
+          <t>A 50627-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10609,10 +10645,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45110</v>
+        <v>44866</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10624,13 +10660,8 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10673,7 +10704,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 38505-2025</t>
+          <t>A 30162-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10683,14 +10714,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45884</v>
+        <v>45110</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10702,8 +10733,13 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10746,7 +10782,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 12807-2022</t>
+          <t>A 38505-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10760,10 +10796,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44642</v>
+        <v>45884</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10776,7 +10812,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10819,7 +10855,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 11337-2025</t>
+          <t>A 12807-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10833,10 +10869,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45726</v>
+        <v>44642</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10849,7 +10885,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10892,7 +10928,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24703-2024</t>
+          <t>A 11337-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10906,10 +10942,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45460</v>
+        <v>45726</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10965,7 +11001,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 57851-2023</t>
+          <t>A 24703-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10979,10 +11015,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45247</v>
+        <v>45460</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10995,7 +11031,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11038,7 +11074,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 54533-2023</t>
+          <t>A 57851-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11052,10 +11088,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45226</v>
+        <v>45247</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11067,13 +11103,8 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11116,7 +11147,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 59056-2023</t>
+          <t>A 54533-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11130,10 +11161,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45252</v>
+        <v>45226</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11145,8 +11176,13 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11189,7 +11225,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 34287-2024</t>
+          <t>A 59056-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11203,10 +11239,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45524</v>
+        <v>45252</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11219,7 +11255,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11262,7 +11298,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 41914-2025</t>
+          <t>A 34287-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11276,10 +11312,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45903</v>
+        <v>45524</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11292,7 +11328,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11335,7 +11371,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 42384-2025</t>
+          <t>A 41914-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11349,10 +11385,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45905</v>
+        <v>45903</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11365,7 +11401,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11408,7 +11444,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 10865-2023</t>
+          <t>A 42384-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11422,10 +11458,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44991</v>
+        <v>45905</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11438,7 +11474,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11481,7 +11517,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 4814-2023</t>
+          <t>A 10865-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11495,10 +11531,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44957</v>
+        <v>44991</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11511,7 +11547,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11554,7 +11590,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7780-2025</t>
+          <t>A 4814-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11568,10 +11604,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45706</v>
+        <v>44957</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11584,7 +11620,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11627,7 +11663,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 43303-2025</t>
+          <t>A 7780-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11641,10 +11677,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45910</v>
+        <v>45706</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11657,7 +11693,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11700,7 +11736,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 49406-2023</t>
+          <t>A 43303-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11714,10 +11750,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45211</v>
+        <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11730,7 +11766,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11773,7 +11809,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 58400-2024</t>
+          <t>A 49406-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11787,10 +11823,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45634</v>
+        <v>45211</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11803,7 +11839,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11846,7 +11882,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 19856-2024</t>
+          <t>A 58400-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11860,10 +11896,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45433</v>
+        <v>45634</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11876,7 +11912,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11919,7 +11955,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 36393-2024</t>
+          <t>A 19856-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11933,10 +11969,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45534</v>
+        <v>45433</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11949,7 +11985,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11992,7 +12028,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 19847-2023</t>
+          <t>A 36393-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12006,10 +12042,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45053</v>
+        <v>45534</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12022,7 +12058,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12065,7 +12101,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 10887-2023</t>
+          <t>A 19847-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12079,10 +12115,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44991</v>
+        <v>45053</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12095,7 +12131,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12138,7 +12174,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 48815-2024</t>
+          <t>A 10887-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12152,10 +12188,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45593</v>
+        <v>44991</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12168,7 +12204,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12211,7 +12247,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 2860-2024</t>
+          <t>A 48815-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12225,10 +12261,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45315</v>
+        <v>45593</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12241,7 +12277,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12284,7 +12320,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 12959-2023</t>
+          <t>A 2860-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12298,10 +12334,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45001</v>
+        <v>45315</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12314,7 +12350,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12357,7 +12393,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 2868-2024</t>
+          <t>A 12959-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12371,10 +12407,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45315</v>
+        <v>45001</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12387,7 +12423,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12430,7 +12466,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 40111-2022</t>
+          <t>A 2868-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12444,10 +12480,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44820</v>
+        <v>45315</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12460,7 +12496,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12503,7 +12539,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 15058-2023</t>
+          <t>A 40111-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12517,10 +12553,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45015</v>
+        <v>44820</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12533,7 +12569,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12576,7 +12612,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 17883-2024</t>
+          <t>A 15058-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12590,10 +12626,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45419</v>
+        <v>45015</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12606,7 +12642,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12649,7 +12685,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 50791-2025</t>
+          <t>A 17883-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12663,10 +12699,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45946</v>
+        <v>45419</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12679,7 +12715,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12722,7 +12758,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 995-2023</t>
+          <t>A 50791-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12736,10 +12772,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44935</v>
+        <v>45946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12751,13 +12787,8 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12800,7 +12831,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 3599-2024</t>
+          <t>A 995-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12814,10 +12845,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45320</v>
+        <v>44935</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12829,8 +12860,13 @@
           <t>SÄVSJÖ</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12873,7 +12909,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 18174-2026</t>
+          <t>A 3599-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12887,10 +12923,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46125</v>
+        <v>45320</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12903,7 +12939,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12963,7 +12999,7 @@
         <v>45054</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13036,7 +13072,7 @@
         <v>45953</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13109,7 +13145,7 @@
         <v>45694</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13182,7 +13218,7 @@
         <v>45953</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13255,7 +13291,7 @@
         <v>45957</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13328,7 +13364,7 @@
         <v>45953</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13401,7 +13437,7 @@
         <v>45953</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13474,7 +13510,7 @@
         <v>45954</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13547,7 +13583,7 @@
         <v>44935</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13625,7 +13661,7 @@
         <v>45959</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13698,7 +13734,7 @@
         <v>45959</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13771,7 +13807,7 @@
         <v>44951</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13844,7 +13880,7 @@
         <v>45166</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13917,7 +13953,7 @@
         <v>45964</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13990,7 +14026,7 @@
         <v>45966</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14063,7 +14099,7 @@
         <v>45747</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14136,7 +14172,7 @@
         <v>44970</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14209,7 +14245,7 @@
         <v>45967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14282,7 +14318,7 @@
         <v>45971</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14355,7 +14391,7 @@
         <v>44866</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14428,7 +14464,7 @@
         <v>45975</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14501,7 +14537,7 @@
         <v>45975</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14574,7 +14610,7 @@
         <v>45975</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14647,7 +14683,7 @@
         <v>45771</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14720,7 +14756,7 @@
         <v>45338</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14793,7 +14829,7 @@
         <v>45978</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14866,7 +14902,7 @@
         <v>45170</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14939,7 +14975,7 @@
         <v>45632</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15012,7 +15048,7 @@
         <v>45632</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15085,7 +15121,7 @@
         <v>45981</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15158,7 +15194,7 @@
         <v>45534</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15231,7 +15267,7 @@
         <v>44886</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15304,7 +15340,7 @@
         <v>46164</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15377,7 +15413,7 @@
         <v>46165</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15450,7 +15486,7 @@
         <v>45986</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15523,7 +15559,7 @@
         <v>45209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15596,7 +15632,7 @@
         <v>45986</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15669,7 +15705,7 @@
         <v>45989</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15747,7 +15783,7 @@
         <v>45204</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15820,7 +15856,7 @@
         <v>45197</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15893,7 +15929,7 @@
         <v>45993</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15966,7 +16002,7 @@
         <v>46168</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16039,7 +16075,7 @@
         <v>44656</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16112,7 +16148,7 @@
         <v>45407</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16185,7 +16221,7 @@
         <v>45407</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16258,7 +16294,7 @@
         <v>45301</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16331,7 +16367,7 @@
         <v>45607</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16404,7 +16440,7 @@
         <v>44826</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16482,7 +16518,7 @@
         <v>45315</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16555,7 +16591,7 @@
         <v>44505</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16628,7 +16664,7 @@
         <v>45446</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16701,7 +16737,7 @@
         <v>46008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16774,7 +16810,7 @@
         <v>45719</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16847,7 +16883,7 @@
         <v>46010</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16920,7 +16956,7 @@
         <v>45407</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16993,7 +17029,7 @@
         <v>45669</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17066,7 +17102,7 @@
         <v>46014</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17139,7 +17175,7 @@
         <v>46014</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17212,7 +17248,7 @@
         <v>46014</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17285,7 +17321,7 @@
         <v>46014</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17358,7 +17394,7 @@
         <v>45607</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17436,7 +17472,7 @@
         <v>46017</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17509,7 +17545,7 @@
         <v>45226</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17587,7 +17623,7 @@
         <v>45067</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17660,7 +17696,7 @@
         <v>45240</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17733,7 +17769,7 @@
         <v>45771</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17806,7 +17842,7 @@
         <v>45546</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17879,7 +17915,7 @@
         <v>44601</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17957,7 +17993,7 @@
         <v>45755</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18030,7 +18066,7 @@
         <v>45084</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18103,7 +18139,7 @@
         <v>45037</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18176,7 +18212,7 @@
         <v>45281</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18249,7 +18285,7 @@
         <v>46066</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18322,7 +18358,7 @@
         <v>46066</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18395,7 +18431,7 @@
         <v>46066</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18468,7 +18504,7 @@
         <v>45237</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18541,7 +18577,7 @@
         <v>45601</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18614,7 +18650,7 @@
         <v>46070</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18692,7 +18728,7 @@
         <v>46070</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18770,7 +18806,7 @@
         <v>44830</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18843,7 +18879,7 @@
         <v>44806</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18916,7 +18952,7 @@
         <v>45469</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18989,7 +19025,7 @@
         <v>45534</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19062,7 +19098,7 @@
         <v>45163</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19135,7 +19171,7 @@
         <v>46087</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19208,7 +19244,7 @@
         <v>46191</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19286,7 +19322,7 @@
         <v>46191</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19364,7 +19400,7 @@
         <v>45161</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19437,7 +19473,7 @@
         <v>45660</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19510,7 +19546,7 @@
         <v>46097</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19583,7 +19619,7 @@
         <v>45127</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19656,7 +19692,7 @@
         <v>46101</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19729,7 +19765,7 @@
         <v>46101</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19802,7 +19838,7 @@
         <v>46101</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19875,7 +19911,7 @@
         <v>45411</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19948,7 +19984,7 @@
         <v>45253</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20021,7 +20057,7 @@
         <v>44510</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20094,7 +20130,7 @@
         <v>46108</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20167,7 +20203,7 @@
         <v>45268</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20240,7 +20276,7 @@
         <v>45341</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20313,7 +20349,7 @@
         <v>45355</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20386,7 +20422,7 @@
         <v>45252</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20459,7 +20495,7 @@
         <v>46125</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20532,7 +20568,7 @@
         <v>46125</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20605,7 +20641,7 @@
         <v>45161</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20678,7 +20714,7 @@
         <v>45541</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20751,7 +20787,7 @@
         <v>45079</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20824,7 +20860,7 @@
         <v>45061</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20897,7 +20933,7 @@
         <v>45785</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20970,7 +21006,7 @@
         <v>45748</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21043,7 +21079,7 @@
         <v>45238</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21116,7 +21152,7 @@
         <v>45244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21189,7 +21225,7 @@
         <v>45211</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21262,7 +21298,7 @@
         <v>45985</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21335,7 +21371,7 @@
         <v>45301</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21408,7 +21444,7 @@
         <v>45274</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21481,7 +21517,7 @@
         <v>44872</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21554,7 +21590,7 @@
         <v>45008</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21632,7 +21668,7 @@
         <v>45104</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21705,7 +21741,7 @@
         <v>45170</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21778,7 +21814,7 @@
         <v>46099</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21851,7 +21887,7 @@
         <v>44590</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21924,7 +21960,7 @@
         <v>45623</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21997,7 +22033,7 @@
         <v>45611</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22070,7 +22106,7 @@
         <v>44896</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22143,7 +22179,7 @@
         <v>45238</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22216,7 +22252,7 @@
         <v>44972</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22289,7 +22325,7 @@
         <v>46226</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22362,7 +22398,7 @@
         <v>45146</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22435,7 +22471,7 @@
         <v>45454</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22508,7 +22544,7 @@
         <v>45601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22581,7 +22617,7 @@
         <v>45253</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22654,7 +22690,7 @@
         <v>45111</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22727,7 +22763,7 @@
         <v>46274</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22800,7 +22836,7 @@
         <v>45029</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22873,7 +22909,7 @@
         <v>45148</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22946,7 +22982,7 @@
         <v>45160</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23019,7 +23055,7 @@
         <v>44942</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23092,7 +23128,7 @@
         <v>46276</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23165,7 +23201,7 @@
         <v>45334</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23238,7 +23274,7 @@
         <v>45267</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23311,7 +23347,7 @@
         <v>44944</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23384,7 +23420,7 @@
         <v>45427</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23457,7 +23493,7 @@
         <v>44651</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23530,7 +23566,7 @@
         <v>44964</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23603,7 +23639,7 @@
         <v>45210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23676,7 +23712,7 @@
         <v>45094</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23749,7 +23785,7 @@
         <v>45694</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23822,7 +23858,7 @@
         <v>45694</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23895,7 +23931,7 @@
         <v>45695</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23968,7 +24004,7 @@
         <v>44839</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24041,7 +24077,7 @@
         <v>45623</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24119,7 +24155,7 @@
         <v>45704</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24192,7 +24228,7 @@
         <v>45317</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24265,7 +24301,7 @@
         <v>46272</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24338,7 +24374,7 @@
         <v>45371</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24411,7 +24447,7 @@
         <v>45371</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24484,7 +24520,7 @@
         <v>44830</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24557,7 +24593,7 @@
         <v>46286</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24630,7 +24666,7 @@
         <v>45275</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24703,7 +24739,7 @@
         <v>44883</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24776,7 +24812,7 @@
         <v>45261</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24849,7 +24885,7 @@
         <v>46282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24922,7 +24958,7 @@
         <v>46282</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24995,7 +25031,7 @@
         <v>46286</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25068,7 +25104,7 @@
         <v>45301</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25141,7 +25177,7 @@
         <v>45532</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25214,7 +25250,7 @@
         <v>45015</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25287,7 +25323,7 @@
         <v>45758</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25365,7 +25401,7 @@
         <v>45334</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25438,7 +25474,7 @@
         <v>45118</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25511,7 +25547,7 @@
         <v>45685</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25584,7 +25620,7 @@
         <v>45607</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25657,7 +25693,7 @@
         <v>45066</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25730,7 +25766,7 @@
         <v>45448</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25803,7 +25839,7 @@
         <v>45607</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25876,7 +25912,7 @@
         <v>46293</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25949,7 +25985,7 @@
         <v>46293</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26022,7 +26058,7 @@
         <v>46294</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26100,7 +26136,7 @@
         <v>45366</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26173,7 +26209,7 @@
         <v>46295</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26246,7 +26282,7 @@
         <v>46251</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26319,7 +26355,7 @@
         <v>45198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26392,7 +26428,7 @@
         <v>46294</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26470,7 +26506,7 @@
         <v>45267</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26543,7 +26579,7 @@
         <v>45211</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26616,7 +26652,7 @@
         <v>46296</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26689,7 +26725,7 @@
         <v>45981</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26762,7 +26798,7 @@
         <v>46301</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26835,7 +26871,7 @@
         <v>45104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26908,7 +26944,7 @@
         <v>45223</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26981,7 +27017,7 @@
         <v>45414</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27054,7 +27090,7 @@
         <v>45644</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27127,7 +27163,7 @@
         <v>45573</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27200,7 +27236,7 @@
         <v>45448</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27273,7 +27309,7 @@
         <v>46184</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27346,7 +27382,7 @@
         <v>45646</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27419,7 +27455,7 @@
         <v>45725</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27492,7 +27528,7 @@
         <v>45412</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27565,7 +27601,7 @@
         <v>46260</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27638,7 +27674,7 @@
         <v>46260</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27711,7 +27747,7 @@
         <v>46303</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27784,7 +27820,7 @@
         <v>45791</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27857,7 +27893,7 @@
         <v>45611</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27930,7 +27966,7 @@
         <v>45791</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28003,7 +28039,7 @@
         <v>45646</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28076,7 +28112,7 @@
         <v>46289</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28149,7 +28185,7 @@
         <v>46273</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28222,7 +28258,7 @@
         <v>45733</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28295,7 +28331,7 @@
         <v>45733</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28368,7 +28404,7 @@
         <v>45548</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28441,7 +28477,7 @@
         <v>45727</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28514,7 +28550,7 @@
         <v>46248</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28587,7 +28623,7 @@
         <v>46248</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28660,7 +28696,7 @@
         <v>46308</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28733,7 +28769,7 @@
         <v>46266</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28806,7 +28842,7 @@
         <v>46266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28879,7 +28915,7 @@
         <v>46308</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -28952,7 +28988,7 @@
         <v>46266</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29025,7 +29061,7 @@
         <v>46248</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29098,7 +29134,7 @@
         <v>46308</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29171,7 +29207,7 @@
         <v>45825</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29244,7 +29280,7 @@
         <v>46282</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29317,7 +29353,7 @@
         <v>45833</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29390,7 +29426,7 @@
         <v>45833</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29463,7 +29499,7 @@
         <v>45832</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29536,7 +29572,7 @@
         <v>45833</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29609,7 +29645,7 @@
         <v>45764</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29682,7 +29718,7 @@
         <v>45839</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29755,7 +29791,7 @@
         <v>45418</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29828,7 +29864,7 @@
         <v>45110</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -29906,7 +29942,7 @@
         <v>45329</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -29979,7 +30015,7 @@
         <v>44833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30052,7 +30088,7 @@
         <v>45881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30125,7 +30161,7 @@
         <v>44882</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30198,7 +30234,7 @@
         <v>45139</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30271,7 +30307,7 @@
         <v>45063</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30344,7 +30380,7 @@
         <v>45063</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30417,7 +30453,7 @@
         <v>45173</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30490,7 +30526,7 @@
         <v>45152</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30563,7 +30599,7 @@
         <v>44558</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30636,7 +30672,7 @@
         <v>45152</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30709,7 +30745,7 @@
         <v>45620</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30782,7 +30818,7 @@
         <v>45600</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30855,7 +30891,7 @@
         <v>45141</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -30928,7 +30964,7 @@
         <v>45762</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31001,7 +31037,7 @@
         <v>45776</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31079,7 +31115,7 @@
         <v>45786</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31152,7 +31188,7 @@
         <v>45785</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31225,7 +31261,7 @@
         <v>45794</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31303,7 +31339,7 @@
         <v>45794</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31381,7 +31417,7 @@
         <v>45712</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31454,7 +31490,7 @@
         <v>45712</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31527,7 +31563,7 @@
         <v>45818</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31600,7 +31636,7 @@
         <v>45840</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31673,7 +31709,7 @@
         <v>45985</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31746,7 +31782,7 @@
         <v>45985</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31819,7 +31855,7 @@
         <v>45985</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31892,7 +31928,7 @@
         <v>46073</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -31965,7 +32001,7 @@
         <v>46091</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32038,7 +32074,7 @@
         <v>46091</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32111,7 +32147,7 @@
         <v>46106</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32184,7 +32220,7 @@
         <v>46119</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32257,7 +32293,7 @@
         <v>46125</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>46309</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44008</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>44847</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45217</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>46302</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46095</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45037</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45890</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45530</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>45981</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45722</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45719</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>46300</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>46300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>46001</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>46314</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>46125</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45168</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45768</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45170</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45218</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45351</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46091</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>46316</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44862</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44876</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44533</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>44805</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>44855</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44809</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44573</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>44603</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44886</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>44862</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44572</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44580</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44826</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>44746</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>44844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>44869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>44857</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>44862</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44883</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44833</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>44662</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44791</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44853</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44789</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44790</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44533</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44565</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44664</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44541</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44624</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44700</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>44816</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44798</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45110</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44789</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44861</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45726</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45460</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>45198</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45669</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44935</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>45334</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>45198</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>45881</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45338</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44781</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44929</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>45261</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45884</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45905</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45910</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44893</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45706</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>46164</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>45607</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>46168</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>46165</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45268</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>45210</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45211</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44806</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45267</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>45419</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44995</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45448</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45446</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45053</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>45317</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45371</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>45454</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45253</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>45365</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>45771</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45407</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>45407</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>45953</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45953</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45954</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45953</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>45953</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45212</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45957</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>45764</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45959</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>45959</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45301</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45315</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>45964</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>45102</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44866</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44664</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44642</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>46191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45228</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45966</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>46191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>45967</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45971</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45366</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45371</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>45015</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45094</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45611</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44935</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45975</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45975</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>45975</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>45341</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45334</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45719</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45252</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45321</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44964</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45253</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45989</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45747</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45350</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45694</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45694</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44883</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45993</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45646</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>46099</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45315</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>46226</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>45223</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>46008</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45412</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45244</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46276</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45725</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45448</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>46010</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>45573</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>46014</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>46014</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>46014</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>46014</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45644</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45414</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>46017</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45646</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>45226</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45611</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>46286</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45791</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>46286</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45733</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45733</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>46282</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>46282</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45160</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45646</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45548</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45727</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>46293</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>46293</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>46066</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>46066</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>46066</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>46070</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>46070</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>46251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>46294</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>46295</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45825</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>46296</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>46294</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45832</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45455</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45833</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>46087</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45833</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45833</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45764</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>45839</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45546</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>46097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44951</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>46184</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>45981</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>46101</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>46101</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>46101</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45418</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>46301</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>44972</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>46108</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45329</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45110</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>44833</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>46289</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>46303</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>46125</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>46125</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>46260</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>46260</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>46248</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>46308</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45534</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>46248</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>46308</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>46308</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>45660</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45879</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>44896</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>45029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45247</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45985</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>46266</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46266</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46282</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46266</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45001</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45127</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45671</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>46248</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44590</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>46272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>46316</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45785</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>46273</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>46316</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44957</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>46316</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>46316</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>46316</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46316</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45320</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45320</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>46316</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>44942</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45209</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>46318</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>44944</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45541</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>46317</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45061</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>45037</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>46317</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>46274</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>45601</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>46318</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>45698</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45524</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>45593</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45106</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45623</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>44509</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>44991</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>45671</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>44970</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>45679</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45685</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45098</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45634</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>44991</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44820</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>45067</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>44501</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45748</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>45695</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45274</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45240</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>44886</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45079</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44866</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45015</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45111</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45267</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45066</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45427</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45252</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45086</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44839</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45094</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44826</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45094</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45104</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>44510</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45118</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44505</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45371</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45267</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45146</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45148</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45771</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45166</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45607</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45607</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>45534</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45037</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45634</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45634</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45469</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44988</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45518</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45170</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45607</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45040</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45161</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45758</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45534</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45355</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45411</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45632</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45632</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45054</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45067</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44601</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45084</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>44610</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45601</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>45281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45204</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45371</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45407</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45163</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45201</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>45197</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45211</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>44872</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45238</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45167</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45704</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>44656</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45161</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45694</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45238</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45433</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>45237</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44651</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45211</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45226</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45775</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>45315</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44830</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45302</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45237</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45301</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>45532</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>45301</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>45275</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45320</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>45252</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>45547</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>44838</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45623</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>45534</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>45008</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>44952</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44558</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>44882</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45139</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>45063</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45063</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45173</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45152</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>45152</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45620</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         <v>45600</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>45141</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45762</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45776</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>45786</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45785</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45794</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45794</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45712</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45712</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45818</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45840</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45985</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45985</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45985</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46073</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>46091</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>46091</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>46106</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>46119</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>46125</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>

--- a/Översikt SÄVSJÖ.xlsx
+++ b/Översikt SÄVSJÖ.xlsx
@@ -601,7 +601,7 @@
         <v>44942</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>46309</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44008</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>44847</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>45217</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>46302</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46095</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>45037</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45890</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45530</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45646</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>45981</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45722</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>45719</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>46300</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>46300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>46001</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>46314</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>46125</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>45168</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45768</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45170</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45218</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45351</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46091</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>46316</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44862</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44876</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>44533</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>44805</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>44510</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>44855</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44809</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>44573</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>44603</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44886</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>44862</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>44572</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>44580</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44826</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>44746</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>44844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>44869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>44857</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>44862</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>44883</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>44518</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44833</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>44662</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44791</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44853</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44789</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44790</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44533</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44565</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44664</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44541</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44624</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44700</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>44816</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44798</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45110</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44789</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44861</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45726</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45460</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>45198</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45669</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44935</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>45334</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>45198</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>45881</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45338</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44781</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44929</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>45261</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45884</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45905</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45910</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44893</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45706</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>46164</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>45607</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>46168</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>46165</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45268</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>45210</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45211</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44806</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45267</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>45419</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44995</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45448</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45446</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45053</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>45317</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45371</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>45454</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45253</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>45365</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>45771</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45407</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>45407</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>45953</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45953</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45954</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45953</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>45953</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45212</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45957</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>45764</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45959</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>45959</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45301</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45315</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>45964</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>45102</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44866</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44664</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44642</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>46191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45228</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45966</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>46191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>45967</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45971</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45366</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45371</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>45015</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45094</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45611</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44935</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45975</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45975</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>45975</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>45341</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45334</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45719</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45252</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45321</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44964</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45253</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45989</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45747</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45350</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45694</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45694</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44883</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45993</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45646</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>46099</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45315</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>46226</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>45223</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>46008</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45412</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45244</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46276</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45725</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45448</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>46010</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>45573</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>46014</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>46014</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>46014</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>46014</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45644</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45414</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>46017</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45646</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>45226</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45611</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>46286</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45791</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>46286</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45733</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45733</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>46282</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>46282</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45160</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45646</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45548</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45727</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>46293</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>46293</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>46066</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>46066</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>46066</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>46070</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>46070</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>46251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>46294</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>46295</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45825</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>46296</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>46294</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45832</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45455</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45833</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>46087</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45833</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45833</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45764</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>45839</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45546</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>46097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44951</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>46184</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>45981</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>46101</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>46101</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>46101</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45418</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>46301</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>44972</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>46108</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45329</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45110</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>44833</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>46289</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>46303</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>46125</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>46125</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>46260</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>46260</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>46248</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>46308</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45534</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>46248</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>46308</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>46308</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>45660</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45879</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>44896</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>45029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45247</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45985</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>46266</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46266</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46282</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46266</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45001</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45127</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45671</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>46248</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44590</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>46272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>46316</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45785</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>46273</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>46316</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44957</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>46316</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>46316</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>46316</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>46316</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45320</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45320</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>46316</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>44942</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45209</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>46318</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>44944</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45541</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>46317</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45061</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>45037</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>46317</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>46274</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>45601</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>46318</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>45698</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45524</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>45593</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45106</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45623</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>44509</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>44991</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>45671</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>44970</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>45679</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45685</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45098</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45634</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>44991</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44820</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>45067</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>44501</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45748</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>45695</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45274</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45240</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>44886</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45079</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44866</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45015</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45111</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45267</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45066</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45427</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45252</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45086</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44839</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45094</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44826</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45094</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45104</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>44510</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45118</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44505</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45371</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45267</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45146</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45148</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45771</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45166</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45607</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45607</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>45534</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45037</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45634</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45634</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45469</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44988</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45518</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45170</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45607</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45040</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45161</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45758</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45534</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45355</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45411</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45632</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45632</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45054</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45067</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44601</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45084</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>44610</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45601</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>45281</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45204</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45371</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45407</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45163</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45201</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>45197</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45211</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>44872</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45238</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45167</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45704</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>44656</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45161</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45694</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45238</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45433</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>45237</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44651</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45211</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45226</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45775</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>45315</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>44830</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45302</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45237</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45301</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>45532</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>45301</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>45275</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45320</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>45252</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>45547</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>44838</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45623</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>45534</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>45008</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>44952</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44558</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>44882</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45139</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>45063</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45063</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45173</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>45152</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>45152</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45620</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         <v>45600</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>45141</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45762</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45776</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>45786</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45785</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45794</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45794</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45712</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45712</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45818</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45840</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45985</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45985</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45985</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46073</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>46091</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>46091</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33164,7 +33164,7 @@
         <v>46106</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>46119</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>46125</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
